--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251009_201457.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251009_201457.xlsx
@@ -5180,7 +5180,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251009_201457.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251009_201457.xlsx
@@ -5180,7 +5180,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251009_201457.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251009_201457.xlsx
@@ -5180,7 +5180,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251009_201457.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251009_201457.xlsx
@@ -7438,7 +7438,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251009_201457.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251009_201457.xlsx
@@ -7438,7 +7438,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251009_201457.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251009_201457.xlsx
@@ -5180,7 +5180,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
